--- a/artfynd/A 58469-2023 artfynd.xlsx
+++ b/artfynd/A 58469-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>93707700</v>
       </c>
       <c r="B3" t="n">
-        <v>57945</v>
+        <v>58000</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58469-2023 artfynd.xlsx
+++ b/artfynd/A 58469-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>93707700</v>
       </c>
       <c r="B3" t="n">
-        <v>58000</v>
+        <v>58013</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58469-2023 artfynd.xlsx
+++ b/artfynd/A 58469-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>93707700</v>
       </c>
       <c r="B3" t="n">
-        <v>58013</v>
+        <v>58015</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58469-2023 artfynd.xlsx
+++ b/artfynd/A 58469-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>93707700</v>
       </c>
       <c r="B3" t="n">
-        <v>58015</v>
+        <v>58025</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58469-2023 artfynd.xlsx
+++ b/artfynd/A 58469-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>93707700</v>
       </c>
       <c r="B3" t="n">
-        <v>58025</v>
+        <v>58026</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58469-2023 artfynd.xlsx
+++ b/artfynd/A 58469-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>93707700</v>
       </c>
       <c r="B3" t="n">
-        <v>58026</v>
+        <v>58027</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 58469-2023 artfynd.xlsx
+++ b/artfynd/A 58469-2023 artfynd.xlsx
@@ -807,7 +807,7 @@
         <v>93707700</v>
       </c>
       <c r="B3" t="n">
-        <v>58027</v>
+        <v>58030</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
